--- a/tests/TC-03/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-03/results/timetable_all_departments_even.xlsx
@@ -810,16 +810,9 @@
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="12" t="n"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
@@ -881,8 +874,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>CS163
 LEC
@@ -890,9 +882,10 @@
 Dr. Vivekraj</t>
         </is>
       </c>
+      <c r="E4" s="11" t="n"/>
       <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
@@ -969,10 +962,17 @@
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr">
         <is>
@@ -1062,8 +1062,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1235,16 +1235,9 @@
         </is>
       </c>
       <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="12" t="n"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr"/>
@@ -1306,8 +1299,7 @@
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>CS163
 LEC
@@ -1315,9 +1307,10 @@
 Dr. Vivekraj</t>
         </is>
       </c>
+      <c r="E4" s="11" t="n"/>
       <c r="F4" s="11" t="n"/>
-      <c r="G4" s="11" t="n"/>
-      <c r="H4" s="12" t="n"/>
+      <c r="G4" s="12" t="n"/>
+      <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
@@ -1394,10 +1387,17 @@
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr"/>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr">
         <is>
@@ -1487,8 +1487,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>

--- a/tests/TC-03/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-03/results/timetable_all_departments_even.xlsx
@@ -852,29 +852,7 @@
       <c r="N3" s="8" t="inlineStr"/>
       <c r="O3" s="8" t="inlineStr"/>
       <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>CS163
 LEC
@@ -882,11 +860,40 @@
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="12" t="n"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="12" t="n"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
       <c r="L4" s="9" t="inlineStr">
@@ -962,17 +969,10 @@
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr">
         <is>
@@ -1062,8 +1062,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1277,29 +1277,7 @@
       <c r="N3" s="8" t="inlineStr"/>
       <c r="O3" s="8" t="inlineStr"/>
       <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="Q3" s="10" t="inlineStr">
         <is>
           <t>CS163
 LEC
@@ -1307,11 +1285,40 @@
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n"/>
-      <c r="F4" s="11" t="n"/>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="12" t="n"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="12" t="n"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
       <c r="L4" s="9" t="inlineStr">
@@ -1387,17 +1394,10 @@
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr">
         <is>
@@ -1487,8 +1487,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="Q3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" t="n">
-        <v>7</v>
-      </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>6</v>
       </c>
-      <c r="C5" t="n">
-        <v>7</v>
-      </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
